--- a/B306_2026级考核统计表.xlsx
+++ b/B306_2026级考核统计表.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WilliTourt\Desktop\B306招新\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\WilliTourt\Desktop\2026-Enrollment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41E87F84-C2DF-4E93-89D4-727B509B7716}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51D36C9B-1435-40B9-A2D9-891BFA098E23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-109" yWindow="-14692" windowWidth="23550" windowHeight="14100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-109" yWindow="-109" windowWidth="23550" windowHeight="14099" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
